--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/136.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/136.xlsx
@@ -426,13 +426,13 @@
         <v>-17.36425691397431</v>
       </c>
       <c r="E2">
-        <v>-21.50841052422068</v>
+        <v>-20.83887111371261</v>
       </c>
       <c r="F2">
-        <v>-5.925266619265217</v>
+        <v>-6.620439170633785</v>
       </c>
       <c r="G2">
-        <v>-15.58639053574763</v>
+        <v>-15.66703708035704</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.23274448505668</v>
       </c>
       <c r="E3">
-        <v>-21.37500167995471</v>
+        <v>-21.08926402701873</v>
       </c>
       <c r="F3">
-        <v>-6.202684377360564</v>
+        <v>-6.781137476572472</v>
       </c>
       <c r="G3">
-        <v>-15.62069440862556</v>
+        <v>-15.40780977772272</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.02961058135256</v>
       </c>
       <c r="E4">
-        <v>-21.92046543112662</v>
+        <v>-21.99917030937993</v>
       </c>
       <c r="F4">
-        <v>-6.011925446741685</v>
+        <v>-6.587981250689892</v>
       </c>
       <c r="G4">
-        <v>-15.82519011713188</v>
+        <v>-14.9106850173636</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.75724595441511</v>
       </c>
       <c r="E5">
-        <v>-22.55574240729266</v>
+        <v>-22.78445751552405</v>
       </c>
       <c r="F5">
-        <v>-6.039654217182996</v>
+        <v>-6.59309103501406</v>
       </c>
       <c r="G5">
-        <v>-14.82108344707046</v>
+        <v>-14.99383598967348</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.41855882724029</v>
       </c>
       <c r="E6">
-        <v>-22.40830887902493</v>
+        <v>-22.75559302219916</v>
       </c>
       <c r="F6">
-        <v>-6.000429363925633</v>
+        <v>-6.426501794290365</v>
       </c>
       <c r="G6">
-        <v>-14.09287598697913</v>
+        <v>-15.02031042235103</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.00108117285668</v>
       </c>
       <c r="E7">
-        <v>-24.32705954386692</v>
+        <v>-23.33065487948521</v>
       </c>
       <c r="F7">
-        <v>-6.147819119170943</v>
+        <v>-6.537360961255918</v>
       </c>
       <c r="G7">
-        <v>-14.86893738284062</v>
+        <v>-14.75746634871505</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.50097393666296</v>
       </c>
       <c r="E8">
-        <v>-23.73966665185799</v>
+        <v>-24.29455415743987</v>
       </c>
       <c r="F8">
-        <v>-6.290734033706332</v>
+        <v>-6.320860099411344</v>
       </c>
       <c r="G8">
-        <v>-14.4575954784951</v>
+        <v>-14.00752515715841</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.91251846959592</v>
       </c>
       <c r="E9">
-        <v>-24.66878724943374</v>
+        <v>-23.55614118574914</v>
       </c>
       <c r="F9">
-        <v>-6.315927585711374</v>
+        <v>-6.74211971516581</v>
       </c>
       <c r="G9">
-        <v>-15.2602753157651</v>
+        <v>-14.86423640817486</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.21532317162501</v>
       </c>
       <c r="E10">
-        <v>-25.07477852964341</v>
+        <v>-25.12214636776365</v>
       </c>
       <c r="F10">
-        <v>-6.430913264893974</v>
+        <v>-6.556017037718068</v>
       </c>
       <c r="G10">
-        <v>-14.79288090962141</v>
+        <v>-13.8801386753528</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.41526891068867</v>
       </c>
       <c r="E11">
-        <v>-26.08643056600896</v>
+        <v>-25.33606695141199</v>
       </c>
       <c r="F11">
-        <v>-6.268761588347075</v>
+        <v>-6.645357290477397</v>
       </c>
       <c r="G11">
-        <v>-13.82019462727321</v>
+        <v>-13.791008857799</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.53304955493173</v>
       </c>
       <c r="E12">
-        <v>-26.88299367243218</v>
+        <v>-25.74871508841293</v>
       </c>
       <c r="F12">
-        <v>-6.409999473075494</v>
+        <v>-6.438195028548282</v>
       </c>
       <c r="G12">
-        <v>-12.96361414280557</v>
+        <v>-13.70698390146676</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.5903703103365</v>
       </c>
       <c r="E13">
-        <v>-27.78120290643157</v>
+        <v>-26.49604915389877</v>
       </c>
       <c r="F13">
-        <v>-5.944047365021488</v>
+        <v>-6.433860181929433</v>
       </c>
       <c r="G13">
-        <v>-11.99113476955358</v>
+        <v>-13.76024064755701</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.63946635279542</v>
       </c>
       <c r="E14">
-        <v>-27.05146649093954</v>
+        <v>-27.55760497382884</v>
       </c>
       <c r="F14">
-        <v>-6.269835152501103</v>
+        <v>-5.905017178103783</v>
       </c>
       <c r="G14">
-        <v>-12.7242484581341</v>
+        <v>-12.91317798151477</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.741313947115039</v>
       </c>
       <c r="E15">
-        <v>-29.27408229017022</v>
+        <v>-27.54726646766933</v>
       </c>
       <c r="F15">
-        <v>-5.969086426505909</v>
+        <v>-6.044728795892546</v>
       </c>
       <c r="G15">
-        <v>-12.04879454121107</v>
+        <v>-12.91993811550596</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.943434322419566</v>
       </c>
       <c r="E16">
-        <v>-29.91170501587223</v>
+        <v>-29.0727463357892</v>
       </c>
       <c r="F16">
-        <v>-5.680241340088943</v>
+        <v>-5.869669912658926</v>
       </c>
       <c r="G16">
-        <v>-11.24948649457281</v>
+        <v>-12.44983071729284</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.299594843723346</v>
       </c>
       <c r="E17">
-        <v>-29.97526667704389</v>
+        <v>-28.89629887455433</v>
       </c>
       <c r="F17">
-        <v>-6.000033404307096</v>
+        <v>-5.680365595199363</v>
       </c>
       <c r="G17">
-        <v>-11.72971091995395</v>
+        <v>-12.29942601235267</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.845987797964592</v>
       </c>
       <c r="E18">
-        <v>-30.7761340980114</v>
+        <v>-28.85661585682512</v>
       </c>
       <c r="F18">
-        <v>-5.840593388453261</v>
+        <v>-5.428161684110428</v>
       </c>
       <c r="G18">
-        <v>-11.72049767171816</v>
+        <v>-12.48202908320779</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.586679249547541</v>
       </c>
       <c r="E19">
-        <v>-30.70606501969072</v>
+        <v>-30.55287806519625</v>
       </c>
       <c r="F19">
-        <v>-5.45994448462104</v>
+        <v>-5.476708984118896</v>
       </c>
       <c r="G19">
-        <v>-11.04838409524424</v>
+        <v>-12.41414965747057</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.524278946382648</v>
       </c>
       <c r="E20">
-        <v>-30.50512077831136</v>
+        <v>-30.32316216420916</v>
       </c>
       <c r="F20">
-        <v>-5.130106808909138</v>
+        <v>-5.390512385653191</v>
       </c>
       <c r="G20">
-        <v>-11.3114963230689</v>
+        <v>-12.50896699226084</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.646370630134821</v>
       </c>
       <c r="E21">
-        <v>-32.41439561129231</v>
+        <v>-31.0100999718547</v>
       </c>
       <c r="F21">
-        <v>-4.873737038151525</v>
+        <v>-4.882276677706985</v>
       </c>
       <c r="G21">
-        <v>-11.57700207531845</v>
+        <v>-12.23601251254793</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.915035950941111</v>
       </c>
       <c r="E22">
-        <v>-32.09225355580865</v>
+        <v>-31.04828180045037</v>
       </c>
       <c r="F22">
-        <v>-4.970334617726781</v>
+        <v>-4.788400285049925</v>
       </c>
       <c r="G22">
-        <v>-10.12849935897466</v>
+        <v>-12.77602539036831</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.294907434244179</v>
       </c>
       <c r="E23">
-        <v>-32.25430046969913</v>
+        <v>-30.78144146954839</v>
       </c>
       <c r="F23">
-        <v>-5.349996107614865</v>
+        <v>-4.588992370378417</v>
       </c>
       <c r="G23">
-        <v>-10.55054094650311</v>
+        <v>-12.42385286644618</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.742186357370404</v>
       </c>
       <c r="E24">
-        <v>-32.40454165185161</v>
+        <v>-31.81722800813782</v>
       </c>
       <c r="F24">
-        <v>-5.26676175098157</v>
+        <v>-4.593173969027749</v>
       </c>
       <c r="G24">
-        <v>-10.67604372789688</v>
+        <v>-12.35863511932253</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.200386748870883</v>
       </c>
       <c r="E25">
-        <v>-32.40656587973304</v>
+        <v>-31.76304028816203</v>
       </c>
       <c r="F25">
-        <v>-4.48052594265585</v>
+        <v>-4.615818220350676</v>
       </c>
       <c r="G25">
-        <v>-12.72947580954061</v>
+        <v>-12.57567779542269</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.627240194378299</v>
       </c>
       <c r="E26">
-        <v>-33.23865486474644</v>
+        <v>-32.11094709651232</v>
       </c>
       <c r="F26">
-        <v>-4.404825587551017</v>
+        <v>-4.407892203676181</v>
       </c>
       <c r="G26">
-        <v>-11.28006600371906</v>
+        <v>-13.04143513679722</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.988319658691058</v>
       </c>
       <c r="E27">
-        <v>-33.51060331432907</v>
+        <v>-31.96915604685815</v>
       </c>
       <c r="F27">
-        <v>-4.639797799926916</v>
+        <v>-4.019385406661004</v>
       </c>
       <c r="G27">
-        <v>-11.93099870983272</v>
+        <v>-13.28969956787824</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.25316422134672</v>
       </c>
       <c r="E28">
-        <v>-32.38648889022004</v>
+        <v>-31.47167147779751</v>
       </c>
       <c r="F28">
-        <v>-4.671489480023221</v>
+        <v>-4.398052855665728</v>
       </c>
       <c r="G28">
-        <v>-12.32694657742063</v>
+        <v>-12.89115623258754</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.4147079970597</v>
       </c>
       <c r="E29">
-        <v>-31.75616153614438</v>
+        <v>-31.84135571765069</v>
       </c>
       <c r="F29">
-        <v>-4.690116977809972</v>
+        <v>-4.282322474188012</v>
       </c>
       <c r="G29">
-        <v>-11.5819380987175</v>
+        <v>-13.11346929718622</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.4793308025079</v>
       </c>
       <c r="E30">
-        <v>-32.63757466004932</v>
+        <v>-31.31086310154813</v>
       </c>
       <c r="F30">
-        <v>-3.965367568324449</v>
+        <v>-3.982808015622989</v>
       </c>
       <c r="G30">
-        <v>-13.11025806801313</v>
+        <v>-12.96983465787386</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.45679963073179</v>
       </c>
       <c r="E31">
-        <v>-32.48451223859007</v>
+        <v>-31.22397074228896</v>
       </c>
       <c r="F31">
-        <v>-4.040821069943247</v>
+        <v>-3.930817192321084</v>
       </c>
       <c r="G31">
-        <v>-12.39066464741498</v>
+        <v>-13.5021356198605</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.37268762004455</v>
       </c>
       <c r="E32">
-        <v>-32.35602584557044</v>
+        <v>-31.62314666911708</v>
       </c>
       <c r="F32">
-        <v>-4.312272097636228</v>
+        <v>-4.225035069712607</v>
       </c>
       <c r="G32">
-        <v>-11.98503674467024</v>
+        <v>-13.77416480209519</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.25490636481723</v>
       </c>
       <c r="E33">
-        <v>-31.07098756912483</v>
+        <v>-31.19910489151284</v>
       </c>
       <c r="F33">
-        <v>-4.348871026226716</v>
+        <v>-4.382538362578696</v>
       </c>
       <c r="G33">
-        <v>-12.14444613347723</v>
+        <v>-13.30043235651656</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.12233884787838</v>
       </c>
       <c r="E34">
-        <v>-31.96630763670733</v>
+        <v>-29.80375072400338</v>
       </c>
       <c r="F34">
-        <v>-4.380927187980252</v>
+        <v>-4.172047720425134</v>
       </c>
       <c r="G34">
-        <v>-11.34342322424963</v>
+        <v>-13.02654761350711</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.998170623531578</v>
       </c>
       <c r="E35">
-        <v>-30.1236964695933</v>
+        <v>-30.83864288897628</v>
       </c>
       <c r="F35">
-        <v>-4.022647517493229</v>
+        <v>-4.40246805392265</v>
       </c>
       <c r="G35">
-        <v>-12.60327450303806</v>
+        <v>-12.78418257457707</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.895226745844344</v>
       </c>
       <c r="E36">
-        <v>-32.03121878313328</v>
+        <v>-30.38703176161334</v>
       </c>
       <c r="F36">
-        <v>-4.288714157068013</v>
+        <v>-4.047418187939143</v>
       </c>
       <c r="G36">
-        <v>-11.18742700789363</v>
+        <v>-13.11995134535211</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.808287371727378</v>
       </c>
       <c r="E37">
-        <v>-29.53252909449898</v>
+        <v>-29.73006339495057</v>
       </c>
       <c r="F37">
-        <v>-4.616596057341905</v>
+        <v>-4.177826411427064</v>
       </c>
       <c r="G37">
-        <v>-12.29131517578145</v>
+        <v>-12.91280388986883</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.733329483866255</v>
       </c>
       <c r="E38">
-        <v>-30.94526128101288</v>
+        <v>-30.06880457190933</v>
       </c>
       <c r="F38">
-        <v>-3.770180185570204</v>
+        <v>-4.062106798725583</v>
       </c>
       <c r="G38">
-        <v>-11.95828422616739</v>
+        <v>-12.93308429184241</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.658181805177787</v>
       </c>
       <c r="E39">
-        <v>-29.77335334222689</v>
+        <v>-29.53614960946811</v>
       </c>
       <c r="F39">
-        <v>-4.302975330274609</v>
+        <v>-4.311278056752869</v>
       </c>
       <c r="G39">
-        <v>-12.13293536663718</v>
+        <v>-12.01705634112607</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.562731716379517</v>
       </c>
       <c r="E40">
-        <v>-27.93290225721452</v>
+        <v>-28.66491649513241</v>
       </c>
       <c r="F40">
-        <v>-4.388582131149522</v>
+        <v>-4.054034358385302</v>
       </c>
       <c r="G40">
-        <v>-12.2634072768854</v>
+        <v>-13.07387848308207</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.438496536933179</v>
       </c>
       <c r="E41">
-        <v>-28.53322394251535</v>
+        <v>-28.59681277453106</v>
       </c>
       <c r="F41">
-        <v>-3.943381040719344</v>
+        <v>-4.239452804358332</v>
       </c>
       <c r="G41">
-        <v>-12.50662974711011</v>
+        <v>-12.4104683308309</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.276547941339711</v>
       </c>
       <c r="E42">
-        <v>-29.88980078709713</v>
+        <v>-28.35033699124158</v>
       </c>
       <c r="F42">
-        <v>-4.206032321492386</v>
+        <v>-4.232333814898674</v>
       </c>
       <c r="G42">
-        <v>-11.2246673346649</v>
+        <v>-11.83545967611489</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.0678243566145</v>
       </c>
       <c r="E43">
-        <v>-28.51373339038634</v>
+        <v>-27.84388604364575</v>
       </c>
       <c r="F43">
-        <v>-4.561985107944945</v>
+        <v>-4.441370672260323</v>
       </c>
       <c r="G43">
-        <v>-12.34997142164626</v>
+        <v>-12.44360689167901</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.820324694980712</v>
       </c>
       <c r="E44">
-        <v>-28.37481339325304</v>
+        <v>-27.02624741919082</v>
       </c>
       <c r="F44">
-        <v>-4.458627221995442</v>
+        <v>-4.32896701427225</v>
       </c>
       <c r="G44">
-        <v>-11.83741951907414</v>
+        <v>-12.42070453763833</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.544568732479908</v>
       </c>
       <c r="E45">
-        <v>-25.73445492376278</v>
+        <v>-26.4193141618388</v>
       </c>
       <c r="F45">
-        <v>-4.094317036816039</v>
+        <v>-4.398219357513692</v>
       </c>
       <c r="G45">
-        <v>-10.73471652648938</v>
+        <v>-12.68502180403928</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.250011491475878</v>
       </c>
       <c r="E46">
-        <v>-26.35746426384204</v>
+        <v>-26.10959371055819</v>
       </c>
       <c r="F46">
-        <v>-4.160546667404666</v>
+        <v>-4.40351262521758</v>
       </c>
       <c r="G46">
-        <v>-10.81853291845265</v>
+        <v>-12.52111007329889</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.957133518989782</v>
       </c>
       <c r="E47">
-        <v>-24.3888596286496</v>
+        <v>-25.61005321429807</v>
       </c>
       <c r="F47">
-        <v>-4.211399313895124</v>
+        <v>-4.402220372069213</v>
       </c>
       <c r="G47">
-        <v>-11.14577372391852</v>
+        <v>-12.13856329405394</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.681654259183599</v>
       </c>
       <c r="E48">
-        <v>-24.59046729147109</v>
+        <v>-25.65848977228411</v>
       </c>
       <c r="F48">
-        <v>-4.186806742440813</v>
+        <v>-4.37679611974249</v>
       </c>
       <c r="G48">
-        <v>-11.49515545795105</v>
+        <v>-12.37200310221011</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.432622616124341</v>
       </c>
       <c r="E49">
-        <v>-25.1083028227222</v>
+        <v>-24.99704727330175</v>
       </c>
       <c r="F49">
-        <v>-4.531060496063634</v>
+        <v>-4.301731122435605</v>
       </c>
       <c r="G49">
-        <v>-10.3944851403274</v>
+        <v>-12.5786374231348</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.224231469564089</v>
       </c>
       <c r="E50">
-        <v>-23.66580271231888</v>
+        <v>-24.37636556886244</v>
       </c>
       <c r="F50">
-        <v>-4.188610098276707</v>
+        <v>-4.79372503071512</v>
       </c>
       <c r="G50">
-        <v>-11.12696320416438</v>
+        <v>-12.73462039730864</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.060745979009008</v>
       </c>
       <c r="E51">
-        <v>-24.02505108382138</v>
+        <v>-23.52748047375459</v>
       </c>
       <c r="F51">
-        <v>-4.57430458795938</v>
+        <v>-4.705700225391437</v>
       </c>
       <c r="G51">
-        <v>-11.22558104523374</v>
+        <v>-12.47363685026574</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.937726216392429</v>
       </c>
       <c r="E52">
-        <v>-23.25089939526212</v>
+        <v>-23.67181652580107</v>
       </c>
       <c r="F52">
-        <v>-3.974791075898696</v>
+        <v>-4.38653109346019</v>
       </c>
       <c r="G52">
-        <v>-11.13455428508593</v>
+        <v>-12.39635878574253</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.85482340946368</v>
       </c>
       <c r="E53">
-        <v>-23.27498634850891</v>
+        <v>-23.12120842815645</v>
       </c>
       <c r="F53">
-        <v>-4.104538262199182</v>
+        <v>-4.80695737160744</v>
       </c>
       <c r="G53">
-        <v>-11.99705733552334</v>
+        <v>-11.86284781936128</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.801267225423733</v>
       </c>
       <c r="E54">
-        <v>-22.40042027730357</v>
+        <v>-22.82005132122434</v>
       </c>
       <c r="F54">
-        <v>-4.276637388702599</v>
+        <v>-4.77417473164165</v>
       </c>
       <c r="G54">
-        <v>-11.46317558804169</v>
+        <v>-12.83072553431368</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.757877070944494</v>
       </c>
       <c r="E55">
-        <v>-22.0062392573059</v>
+        <v>-23.06120614755481</v>
       </c>
       <c r="F55">
-        <v>-4.515888118713958</v>
+        <v>-4.772175881098694</v>
       </c>
       <c r="G55">
-        <v>-12.20491655829755</v>
+        <v>-12.97425092562325</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.712007286473969</v>
       </c>
       <c r="E56">
-        <v>-20.88094516571787</v>
+        <v>-22.69880595814298</v>
       </c>
       <c r="F56">
-        <v>-4.175738097204605</v>
+        <v>-4.839188318882966</v>
       </c>
       <c r="G56">
-        <v>-11.7371927528727</v>
+        <v>-12.6370652413574</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.649512895851874</v>
       </c>
       <c r="E57">
-        <v>-22.67077923250951</v>
+        <v>-22.12156590485925</v>
       </c>
       <c r="F57">
-        <v>-4.789545917167997</v>
+        <v>-4.630824924219793</v>
       </c>
       <c r="G57">
-        <v>-12.79799086002137</v>
+        <v>-12.50477253106258</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.558210637825717</v>
       </c>
       <c r="E58">
-        <v>-20.65607020344498</v>
+        <v>-22.11107795905748</v>
       </c>
       <c r="F58">
-        <v>-4.51469609802133</v>
+        <v>-4.335967547193309</v>
       </c>
       <c r="G58">
-        <v>-12.77445288123715</v>
+        <v>-12.56486555369143</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.436027923021149</v>
       </c>
       <c r="E59">
-        <v>-20.76749783487772</v>
+        <v>-21.02813868486319</v>
       </c>
       <c r="F59">
-        <v>-4.259199426506267</v>
+        <v>-4.793948689913877</v>
       </c>
       <c r="G59">
-        <v>-13.2143912779509</v>
+        <v>-12.9521099970566</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.279124104115708</v>
       </c>
       <c r="E60">
-        <v>-21.54856450324669</v>
+        <v>-21.16840816725078</v>
       </c>
       <c r="F60">
-        <v>-4.224960516646355</v>
+        <v>-4.374320129575523</v>
       </c>
       <c r="G60">
-        <v>-12.1254171177175</v>
+        <v>-13.50880140330383</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.085068775719645</v>
       </c>
       <c r="E61">
-        <v>-20.54451577474003</v>
+        <v>-21.44477187899088</v>
       </c>
       <c r="F61">
-        <v>-4.403708119924641</v>
+        <v>-4.727864851988143</v>
       </c>
       <c r="G61">
-        <v>-13.07973483814104</v>
+        <v>-12.9686329298431</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.860330415961388</v>
       </c>
       <c r="E62">
-        <v>-19.98883578620681</v>
+        <v>-20.78027718852736</v>
       </c>
       <c r="F62">
-        <v>-4.385616575847499</v>
+        <v>-4.526177270224131</v>
       </c>
       <c r="G62">
-        <v>-12.67579200307579</v>
+        <v>-13.4194332264712</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.609975852431999</v>
       </c>
       <c r="E63">
-        <v>-20.00812255700548</v>
+        <v>-21.21397820118997</v>
       </c>
       <c r="F63">
-        <v>-4.319121039322575</v>
+        <v>-4.761158594641461</v>
       </c>
       <c r="G63">
-        <v>-12.80004339825572</v>
+        <v>-13.68586924201728</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.341056676238209</v>
       </c>
       <c r="E64">
-        <v>-20.36958082382372</v>
+        <v>-20.90945190959616</v>
       </c>
       <c r="F64">
-        <v>-4.550894096788863</v>
+        <v>-4.374213270180562</v>
       </c>
       <c r="G64">
-        <v>-12.63156642521667</v>
+        <v>-13.10079652886189</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.068189454111666</v>
       </c>
       <c r="E65">
-        <v>-18.97356097063513</v>
+        <v>-19.60837604245239</v>
       </c>
       <c r="F65">
-        <v>-4.355742333832938</v>
+        <v>-4.75410090436961</v>
       </c>
       <c r="G65">
-        <v>-13.47804312469846</v>
+        <v>-13.89631400085768</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.802156582716693</v>
       </c>
       <c r="E66">
-        <v>-19.7331309728897</v>
+        <v>-20.19541571348872</v>
       </c>
       <c r="F66">
-        <v>-4.379405477061309</v>
+        <v>-4.645960853403745</v>
       </c>
       <c r="G66">
-        <v>-11.91678653783263</v>
+        <v>-13.43491995850391</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.552328783322801</v>
       </c>
       <c r="E67">
-        <v>-20.13617421652038</v>
+        <v>-20.02278575584232</v>
       </c>
       <c r="F67">
-        <v>-4.43112873769211</v>
+        <v>-4.724324409708578</v>
       </c>
       <c r="G67">
-        <v>-13.85124754443158</v>
+        <v>-13.668015469924</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.331419286161596</v>
       </c>
       <c r="E68">
-        <v>-19.71987160099524</v>
+        <v>-19.65164561159568</v>
       </c>
       <c r="F68">
-        <v>-4.038800681847819</v>
+        <v>-4.673454367502661</v>
       </c>
       <c r="G68">
-        <v>-13.6680204357423</v>
+        <v>-13.6229490134979</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.144930782001455</v>
       </c>
       <c r="E69">
-        <v>-18.77815278873015</v>
+        <v>-20.50773550884973</v>
       </c>
       <c r="F69">
-        <v>-4.131610137290073</v>
+        <v>-4.740105637099312</v>
       </c>
       <c r="G69">
-        <v>-12.64034268144128</v>
+        <v>-13.82575303323365</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.994844015396563</v>
       </c>
       <c r="E70">
-        <v>-20.20536024240957</v>
+        <v>-19.62346944631995</v>
       </c>
       <c r="F70">
-        <v>-4.205203954089587</v>
+        <v>-4.873316227510903</v>
       </c>
       <c r="G70">
-        <v>-13.26815122696313</v>
+        <v>-13.76614335025353</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.885084039812142</v>
       </c>
       <c r="E71">
-        <v>-19.41935300889822</v>
+        <v>-20.51365875285176</v>
       </c>
       <c r="F71">
-        <v>-4.553621910646282</v>
+        <v>-4.926878463775919</v>
       </c>
       <c r="G71">
-        <v>-12.92149407190942</v>
+        <v>-13.41132901099106</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.811703745562105</v>
       </c>
       <c r="E72">
-        <v>-20.3777773617776</v>
+        <v>-20.3584679486089</v>
       </c>
       <c r="F72">
-        <v>-4.42061841208539</v>
+        <v>-4.889842157196753</v>
       </c>
       <c r="G72">
-        <v>-13.4130769790358</v>
+        <v>-12.98861207217261</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.767471093837577</v>
       </c>
       <c r="E73">
-        <v>-19.84456766127045</v>
+        <v>-20.43764831663302</v>
       </c>
       <c r="F73">
-        <v>-4.846192993641039</v>
+        <v>-5.110486926973832</v>
       </c>
       <c r="G73">
-        <v>-12.56602093408464</v>
+        <v>-13.54300099399727</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.747262891315152</v>
       </c>
       <c r="E74">
-        <v>-19.12301872678429</v>
+        <v>-19.67169316602763</v>
       </c>
       <c r="F74">
-        <v>-4.510882294498841</v>
+        <v>-5.162773477438537</v>
       </c>
       <c r="G74">
-        <v>-12.54927950529254</v>
+        <v>-13.45429658154527</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.740449515139314</v>
       </c>
       <c r="E75">
-        <v>-19.54691559322029</v>
+        <v>-20.76096777535865</v>
       </c>
       <c r="F75">
-        <v>-4.715931391183414</v>
+        <v>-5.216626470661936</v>
       </c>
       <c r="G75">
-        <v>-11.9763929102672</v>
+        <v>-13.23635012651289</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.736568999645161</v>
       </c>
       <c r="E76">
-        <v>-21.32403370499838</v>
+        <v>-20.60042431483873</v>
       </c>
       <c r="F76">
-        <v>-5.048750361177991</v>
+        <v>-4.976040412397264</v>
       </c>
       <c r="G76">
-        <v>-12.29578110171393</v>
+        <v>-13.57948982693111</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.729212329638194</v>
       </c>
       <c r="E77">
-        <v>-20.86735974369486</v>
+        <v>-20.97693975773247</v>
       </c>
       <c r="F77">
-        <v>-4.959860740285784</v>
+        <v>-5.262578495597433</v>
       </c>
       <c r="G77">
-        <v>-12.48667708914493</v>
+        <v>-13.06205652496134</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.709422706061178</v>
       </c>
       <c r="E78">
-        <v>-20.7693771515909</v>
+        <v>-22.42643636047763</v>
       </c>
       <c r="F78">
-        <v>-4.711485543332588</v>
+        <v>-5.354789041407463</v>
       </c>
       <c r="G78">
-        <v>-12.78890672306161</v>
+        <v>-12.47067391200809</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.670327222595296</v>
       </c>
       <c r="E79">
-        <v>-21.76210469507839</v>
+        <v>-22.17014737401353</v>
       </c>
       <c r="F79">
-        <v>-5.34753005785673</v>
+        <v>-5.384635947297731</v>
       </c>
       <c r="G79">
-        <v>-12.75422875853774</v>
+        <v>-13.42242927018424</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.608913231374689</v>
       </c>
       <c r="E80">
-        <v>-21.88617582594054</v>
+        <v>-22.92897470653084</v>
       </c>
       <c r="F80">
-        <v>-5.173606866332348</v>
+        <v>-5.416564540471235</v>
       </c>
       <c r="G80">
-        <v>-11.16238935198013</v>
+        <v>-13.41733765114484</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.51999812668327</v>
       </c>
       <c r="E81">
-        <v>-21.96571394341126</v>
+        <v>-22.76740328241117</v>
       </c>
       <c r="F81">
-        <v>-5.502357724011778</v>
+        <v>-5.568672676442892</v>
       </c>
       <c r="G81">
-        <v>-13.33792428474881</v>
+        <v>-13.72779233545385</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.401392626890308</v>
       </c>
       <c r="E82">
-        <v>-23.18802606213962</v>
+        <v>-22.84896562776332</v>
       </c>
       <c r="F82">
-        <v>-5.38876038859627</v>
+        <v>-5.575243286681897</v>
       </c>
       <c r="G82">
-        <v>-12.40921363407152</v>
+        <v>-11.89439731835053</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.257082479387313</v>
       </c>
       <c r="E83">
-        <v>-23.86274151843846</v>
+        <v>-24.42913587647382</v>
       </c>
       <c r="F83">
-        <v>-5.180179961673563</v>
+        <v>-5.95459662389614</v>
       </c>
       <c r="G83">
-        <v>-12.11602510002258</v>
+        <v>-13.06489366248849</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.091563522496768</v>
       </c>
       <c r="E84">
-        <v>-24.72628075543513</v>
+        <v>-24.99145913637629</v>
       </c>
       <c r="F84">
-        <v>-5.778728425709985</v>
+        <v>-5.938178381972653</v>
       </c>
       <c r="G84">
-        <v>-11.8567630366601</v>
+        <v>-12.04394128145049</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.913204834294952</v>
       </c>
       <c r="E85">
-        <v>-24.09999732864832</v>
+        <v>-25.51476959270267</v>
       </c>
       <c r="F85">
-        <v>-5.587598386494652</v>
+        <v>-5.72902803827682</v>
       </c>
       <c r="G85">
-        <v>-11.42459117978148</v>
+        <v>-12.00200991165008</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.73750827131919</v>
       </c>
       <c r="E86">
-        <v>-25.11678465453856</v>
+        <v>-26.6487402404894</v>
       </c>
       <c r="F86">
-        <v>-5.746984558467305</v>
+        <v>-5.810244491916895</v>
       </c>
       <c r="G86">
-        <v>-11.15425865213568</v>
+        <v>-11.86990259190547</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.578989786096698</v>
       </c>
       <c r="E87">
-        <v>-27.16100122023707</v>
+        <v>-27.12892603884074</v>
       </c>
       <c r="F87">
-        <v>-6.213744738922743</v>
+        <v>-5.986893012196487</v>
       </c>
       <c r="G87">
-        <v>-11.4820092816146</v>
+        <v>-11.6829031165742</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.452662688050698</v>
       </c>
       <c r="E88">
-        <v>-26.58259734913337</v>
+        <v>-28.5703891286963</v>
       </c>
       <c r="F88">
-        <v>-6.100787731509599</v>
+        <v>-6.378256848383919</v>
       </c>
       <c r="G88">
-        <v>-12.62940463897952</v>
+        <v>-12.30102500584814</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.378306233962637</v>
       </c>
       <c r="E89">
-        <v>-28.94412408854934</v>
+        <v>-29.2332716824131</v>
       </c>
       <c r="F89">
-        <v>-6.001501271344856</v>
+        <v>-6.531982785893242</v>
       </c>
       <c r="G89">
-        <v>-11.21016383465735</v>
+        <v>-12.13993054936166</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.369926400411129</v>
       </c>
       <c r="E90">
-        <v>-30.11199942123149</v>
+        <v>-31.23717350825832</v>
       </c>
       <c r="F90">
-        <v>-5.93315599040948</v>
+        <v>-6.313847969346646</v>
       </c>
       <c r="G90">
-        <v>-11.6639701066351</v>
+        <v>-12.0807214423918</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.438672071985251</v>
       </c>
       <c r="E91">
-        <v>-31.30849018116811</v>
+        <v>-32.50682403002586</v>
       </c>
       <c r="F91">
-        <v>-6.147308844850819</v>
+        <v>-6.600993660036768</v>
       </c>
       <c r="G91">
-        <v>-12.00909116855859</v>
+        <v>-12.09717154317643</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.599323850739347</v>
       </c>
       <c r="E92">
-        <v>-32.34374915253564</v>
+        <v>-33.74440616310808</v>
       </c>
       <c r="F92">
-        <v>-6.283231095955474</v>
+        <v>-6.508598802479615</v>
       </c>
       <c r="G92">
-        <v>-11.66732037872085</v>
+        <v>-12.22921596255581</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.85701140551227</v>
       </c>
       <c r="E93">
-        <v>-34.26323343016688</v>
+        <v>-34.98848892062832</v>
       </c>
       <c r="F93">
-        <v>-6.738467443286867</v>
+        <v>-6.816993359602649</v>
       </c>
       <c r="G93">
-        <v>-12.04026988644744</v>
+        <v>-12.19469028312675</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.211468261020642</v>
       </c>
       <c r="E94">
-        <v>-35.86495695091688</v>
+        <v>-37.20506599976977</v>
       </c>
       <c r="F94">
-        <v>-6.993272842204293</v>
+        <v>-6.635745743502715</v>
       </c>
       <c r="G94">
-        <v>-12.65836529135707</v>
+        <v>-12.49381462532759</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.661128663218179</v>
       </c>
       <c r="E95">
-        <v>-37.27649814876676</v>
+        <v>-39.40419260432267</v>
       </c>
       <c r="F95">
-        <v>-6.889987438402535</v>
+        <v>-7.189395037572598</v>
       </c>
       <c r="G95">
-        <v>-12.31742213790415</v>
+        <v>-12.47494120520821</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.19899615185632</v>
       </c>
       <c r="E96">
-        <v>-38.26539913171777</v>
+        <v>-40.09132060787653</v>
       </c>
       <c r="F96">
-        <v>-7.376100766489578</v>
+        <v>-7.145547480023913</v>
       </c>
       <c r="G96">
-        <v>-12.16469011944987</v>
+        <v>-13.15712546121259</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.797393692082332</v>
       </c>
       <c r="E97">
-        <v>-41.05818377206921</v>
+        <v>-42.29006229213877</v>
       </c>
       <c r="F97">
-        <v>-7.222182647742804</v>
+        <v>-7.165084111035237</v>
       </c>
       <c r="G97">
-        <v>-12.26465204200816</v>
+        <v>-13.98940654142198</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.459619256367706</v>
       </c>
       <c r="E98">
-        <v>-43.76906869575492</v>
+        <v>-44.2805711561063</v>
       </c>
       <c r="F98">
-        <v>-7.452559077767972</v>
+        <v>-7.444389718441563</v>
       </c>
       <c r="G98">
-        <v>-13.78699316605986</v>
+        <v>-13.94235044712678</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.137426190319017</v>
       </c>
       <c r="E99">
-        <v>-46.14094979098942</v>
+        <v>-45.7846313421699</v>
       </c>
       <c r="F99">
-        <v>-7.344154777600615</v>
+        <v>-7.603173667312381</v>
       </c>
       <c r="G99">
-        <v>-13.85261148919376</v>
+        <v>-14.11556150028699</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.851864948491912</v>
       </c>
       <c r="E100">
-        <v>-46.84406557202737</v>
+        <v>-48.23927482836858</v>
       </c>
       <c r="F100">
-        <v>-8.203130770117264</v>
+        <v>-7.857143243520383</v>
       </c>
       <c r="G100">
-        <v>-14.50222328763725</v>
+        <v>-14.32152543573998</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.522411898378691</v>
       </c>
       <c r="E101">
-        <v>-48.54679444128146</v>
+        <v>-49.94056930348074</v>
       </c>
       <c r="F101">
-        <v>-7.836580679480691</v>
+        <v>-7.798736300500094</v>
       </c>
       <c r="G101">
-        <v>-14.35312790345786</v>
+        <v>-14.50695571248563</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.247387183366678</v>
       </c>
       <c r="E102">
-        <v>-50.51991962565205</v>
+        <v>-52.12411795744725</v>
       </c>
       <c r="F102">
-        <v>-8.010643450912443</v>
+        <v>-7.603508741926814</v>
       </c>
       <c r="G102">
-        <v>-14.2295270304764</v>
+        <v>-15.03787783225517</v>
       </c>
     </row>
   </sheetData>
